--- a/result/全部明细.xlsx
+++ b/result/全部明细.xlsx
@@ -10708,7 +10708,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -10717,19 +10717,19 @@
         </is>
       </c>
       <c r="H214" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I214" t="n">
         <v>3.95</v>
       </c>
       <c r="J214" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="K214" t="n">
-        <v>-16.96</v>
+        <v>-15.7</v>
       </c>
       <c r="L214" t="n">
-        <v>-16962.03</v>
+        <v>-15696.2</v>
       </c>
     </row>
     <row r="215">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -13137,19 +13137,19 @@
         </is>
       </c>
       <c r="H264" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I264" t="n">
         <v>9.16</v>
       </c>
       <c r="J264" t="n">
-        <v>5.49</v>
+        <v>5.4</v>
       </c>
       <c r="K264" t="n">
-        <v>-40.07</v>
+        <v>-41.05</v>
       </c>
       <c r="L264" t="n">
-        <v>-40065.5</v>
+        <v>-41048.03</v>
       </c>
     </row>
     <row r="265">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -13187,19 +13187,19 @@
         </is>
       </c>
       <c r="H265" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I265" t="n">
         <v>12.59</v>
       </c>
       <c r="J265" t="n">
-        <v>8.699999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K265" t="n">
-        <v>-30.9</v>
+        <v>-30.18</v>
       </c>
       <c r="L265" t="n">
-        <v>-30897.54</v>
+        <v>-30182.68</v>
       </c>
     </row>
     <row r="266">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -13337,7 +13337,7 @@
         </is>
       </c>
       <c r="H268" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I268" t="n">
         <v>5.76</v>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -14213,19 +14213,19 @@
         </is>
       </c>
       <c r="H286" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I286" t="n">
         <v>41.42</v>
       </c>
       <c r="J286" t="n">
-        <v>27</v>
+        <v>26.27</v>
       </c>
       <c r="K286" t="n">
-        <v>-34.81</v>
+        <v>-36.58</v>
       </c>
       <c r="L286" t="n">
-        <v>-34814.1</v>
+        <v>-36576.53</v>
       </c>
     </row>
     <row r="287">
@@ -14742,7 +14742,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -14751,19 +14751,19 @@
         </is>
       </c>
       <c r="H297" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I297" t="n">
         <v>10.64</v>
       </c>
       <c r="J297" t="n">
-        <v>7.65</v>
+        <v>7.55</v>
       </c>
       <c r="K297" t="n">
-        <v>-28.1</v>
+        <v>-29.04</v>
       </c>
       <c r="L297" t="n">
-        <v>-28101.5</v>
+        <v>-29041.35</v>
       </c>
     </row>
     <row r="298">
@@ -16570,7 +16570,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -16579,19 +16579,19 @@
         </is>
       </c>
       <c r="H335" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I335" t="n">
         <v>21.93</v>
       </c>
       <c r="J335" t="n">
-        <v>11.43</v>
+        <v>11.42</v>
       </c>
       <c r="K335" t="n">
-        <v>-47.88</v>
+        <v>-47.93</v>
       </c>
       <c r="L335" t="n">
-        <v>-47879.62</v>
+        <v>-47925.22</v>
       </c>
     </row>
     <row r="336">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -17551,19 +17551,19 @@
         </is>
       </c>
       <c r="H355" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I355" t="n">
         <v>16.39</v>
       </c>
       <c r="J355" t="n">
-        <v>9.960000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="K355" t="n">
-        <v>-39.23</v>
+        <v>-39.48</v>
       </c>
       <c r="L355" t="n">
-        <v>-39231.24</v>
+        <v>-39475.29</v>
       </c>
     </row>
     <row r="356">
@@ -17738,7 +17738,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -17747,19 +17747,19 @@
         </is>
       </c>
       <c r="H359" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I359" t="n">
         <v>11.34</v>
       </c>
       <c r="J359" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="K359" t="n">
-        <v>-59.35</v>
+        <v>-59.08</v>
       </c>
       <c r="L359" t="n">
-        <v>-59347.44</v>
+        <v>-59082.89</v>
       </c>
     </row>
     <row r="360">
@@ -19232,7 +19232,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -19241,19 +19241,19 @@
         </is>
       </c>
       <c r="H390" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I390" t="n">
         <v>17.35</v>
       </c>
       <c r="J390" t="n">
-        <v>13.79</v>
+        <v>12.47</v>
       </c>
       <c r="K390" t="n">
-        <v>-20.52</v>
+        <v>-28.13</v>
       </c>
       <c r="L390" t="n">
-        <v>-20518.73</v>
+        <v>-28126.8</v>
       </c>
     </row>
     <row r="391">
@@ -19328,7 +19328,7 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -19337,19 +19337,19 @@
         </is>
       </c>
       <c r="H392" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I392" t="n">
         <v>27.27</v>
       </c>
       <c r="J392" t="n">
-        <v>15.9</v>
+        <v>15.22</v>
       </c>
       <c r="K392" t="n">
-        <v>-41.69</v>
+        <v>-44.19</v>
       </c>
       <c r="L392" t="n">
-        <v>-41694.17</v>
+        <v>-44187.75</v>
       </c>
     </row>
     <row r="393">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -19633,19 +19633,19 @@
         </is>
       </c>
       <c r="H398" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I398" t="n">
         <v>4.34</v>
       </c>
       <c r="J398" t="n">
-        <v>3.41</v>
+        <v>3.23</v>
       </c>
       <c r="K398" t="n">
-        <v>-21.43</v>
+        <v>-25.58</v>
       </c>
       <c r="L398" t="n">
-        <v>-21428.57</v>
+        <v>-25576.04</v>
       </c>
     </row>
     <row r="399">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -19925,19 +19925,19 @@
         </is>
       </c>
       <c r="H404" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I404" t="n">
         <v>5.18</v>
       </c>
       <c r="J404" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="K404" t="n">
-        <v>-44.4</v>
+        <v>-44.79</v>
       </c>
       <c r="L404" t="n">
-        <v>-44401.54</v>
+        <v>-44787.64</v>
       </c>
     </row>
     <row r="405">
@@ -20016,7 +20016,7 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -20025,19 +20025,19 @@
         </is>
       </c>
       <c r="H406" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I406" t="n">
         <v>15.63</v>
       </c>
       <c r="J406" t="n">
-        <v>11.31</v>
+        <v>10.89</v>
       </c>
       <c r="K406" t="n">
-        <v>-27.64</v>
+        <v>-30.33</v>
       </c>
       <c r="L406" t="n">
-        <v>-27639.16</v>
+        <v>-30326.3</v>
       </c>
     </row>
     <row r="407">
@@ -21164,7 +21164,7 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
@@ -21173,19 +21173,19 @@
         </is>
       </c>
       <c r="H430" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I430" t="n">
         <v>13.47</v>
       </c>
       <c r="J430" t="n">
-        <v>6.99</v>
+        <v>6.94</v>
       </c>
       <c r="K430" t="n">
-        <v>-48.11</v>
+        <v>-48.48</v>
       </c>
       <c r="L430" t="n">
-        <v>-48106.9</v>
+        <v>-48478.1</v>
       </c>
     </row>
     <row r="431">
@@ -21214,7 +21214,7 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
@@ -21223,19 +21223,19 @@
         </is>
       </c>
       <c r="H431" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I431" t="n">
         <v>13.58</v>
       </c>
       <c r="J431" t="n">
-        <v>8.83</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K431" t="n">
-        <v>-34.98</v>
+        <v>-35.27</v>
       </c>
       <c r="L431" t="n">
-        <v>-34977.91</v>
+        <v>-35272.46</v>
       </c>
     </row>
     <row r="432">
@@ -21932,7 +21932,7 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -21941,19 +21941,19 @@
         </is>
       </c>
       <c r="H446" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I446" t="n">
         <v>16.44</v>
       </c>
       <c r="J446" t="n">
-        <v>9.6</v>
+        <v>9.75</v>
       </c>
       <c r="K446" t="n">
-        <v>-41.61</v>
+        <v>-40.69</v>
       </c>
       <c r="L446" t="n">
-        <v>-41605.84</v>
+        <v>-40693.43</v>
       </c>
     </row>
     <row r="447">
@@ -22420,7 +22420,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -22429,19 +22429,19 @@
         </is>
       </c>
       <c r="H456" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I456" t="n">
         <v>11.59</v>
       </c>
       <c r="J456" t="n">
-        <v>7.41</v>
+        <v>7.32</v>
       </c>
       <c r="K456" t="n">
-        <v>-36.07</v>
+        <v>-36.84</v>
       </c>
       <c r="L456" t="n">
-        <v>-36065.57</v>
+        <v>-36842.11</v>
       </c>
     </row>
     <row r="457">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -23155,19 +23155,19 @@
         </is>
       </c>
       <c r="H471" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I471" t="n">
         <v>24.89</v>
       </c>
       <c r="J471" t="n">
-        <v>18.28</v>
+        <v>17.69</v>
       </c>
       <c r="K471" t="n">
-        <v>-26.56</v>
+        <v>-28.93</v>
       </c>
       <c r="L471" t="n">
-        <v>-26556.85</v>
+        <v>-28927.28</v>
       </c>
     </row>
     <row r="472">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -23927,19 +23927,19 @@
         </is>
       </c>
       <c r="H487" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I487" t="n">
         <v>8.52</v>
       </c>
       <c r="J487" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="K487" t="n">
-        <v>-51.29</v>
+        <v>-51.88</v>
       </c>
       <c r="L487" t="n">
-        <v>-51291.08</v>
+        <v>-51877.93</v>
       </c>
     </row>
     <row r="488">
@@ -23968,7 +23968,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -23977,19 +23977,19 @@
         </is>
       </c>
       <c r="H488" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I488" t="n">
         <v>7.88</v>
       </c>
       <c r="J488" t="n">
-        <v>4.43</v>
+        <v>4.37</v>
       </c>
       <c r="K488" t="n">
-        <v>-43.78</v>
+        <v>-44.54</v>
       </c>
       <c r="L488" t="n">
-        <v>-43781.73</v>
+        <v>-44543.15</v>
       </c>
     </row>
     <row r="489">
@@ -24068,7 +24068,7 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -24077,19 +24077,19 @@
         </is>
       </c>
       <c r="H490" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I490" t="n">
         <v>12.68</v>
       </c>
       <c r="J490" t="n">
-        <v>11.2</v>
+        <v>10.97</v>
       </c>
       <c r="K490" t="n">
-        <v>-11.67</v>
+        <v>-13.49</v>
       </c>
       <c r="L490" t="n">
-        <v>-11671.92</v>
+        <v>-13485.8</v>
       </c>
     </row>
     <row r="491">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -24277,19 +24277,19 @@
         </is>
       </c>
       <c r="H494" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I494" t="n">
         <v>82.72</v>
       </c>
       <c r="J494" t="n">
-        <v>62.73</v>
+        <v>61.17</v>
       </c>
       <c r="K494" t="n">
-        <v>-24.17</v>
+        <v>-26.05</v>
       </c>
       <c r="L494" t="n">
-        <v>-24165.86</v>
+        <v>-26051.74</v>
       </c>
     </row>
     <row r="495">
@@ -24418,7 +24418,7 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -24427,19 +24427,19 @@
         </is>
       </c>
       <c r="H497" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I497" t="n">
         <v>31.43</v>
       </c>
       <c r="J497" t="n">
-        <v>23.88</v>
+        <v>23.13</v>
       </c>
       <c r="K497" t="n">
-        <v>-24.02</v>
+        <v>-26.41</v>
       </c>
       <c r="L497" t="n">
-        <v>-24021.64</v>
+        <v>-26407.89</v>
       </c>
     </row>
     <row r="498">
@@ -26708,7 +26708,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
@@ -26717,19 +26717,19 @@
         </is>
       </c>
       <c r="H544" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I544" t="n">
         <v>37.03</v>
       </c>
       <c r="J544" t="n">
-        <v>27.46</v>
+        <v>26.58</v>
       </c>
       <c r="K544" t="n">
-        <v>-25.84</v>
+        <v>-28.22</v>
       </c>
       <c r="L544" t="n">
-        <v>-25843.91</v>
+        <v>-28220.36</v>
       </c>
     </row>
     <row r="545">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -26767,19 +26767,19 @@
         </is>
       </c>
       <c r="H545" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I545" t="n">
         <v>47.26</v>
       </c>
       <c r="J545" t="n">
-        <v>23.71</v>
+        <v>25.03</v>
       </c>
       <c r="K545" t="n">
-        <v>-49.83</v>
+        <v>-47.04</v>
       </c>
       <c r="L545" t="n">
-        <v>-49830.72</v>
+        <v>-47037.66</v>
       </c>
     </row>
     <row r="546">
@@ -26858,7 +26858,7 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -26867,19 +26867,19 @@
         </is>
       </c>
       <c r="H547" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I547" t="n">
         <v>127.39</v>
       </c>
       <c r="J547" t="n">
-        <v>125.32</v>
+        <v>128.71</v>
       </c>
       <c r="K547" t="n">
-        <v>-1.62</v>
+        <v>1.04</v>
       </c>
       <c r="L547" t="n">
-        <v>-1624.93</v>
+        <v>1036.19</v>
       </c>
     </row>
     <row r="548">
@@ -27346,7 +27346,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -27355,19 +27355,19 @@
         </is>
       </c>
       <c r="H557" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I557" t="n">
         <v>12.76</v>
       </c>
       <c r="J557" t="n">
-        <v>9.869999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="K557" t="n">
-        <v>-22.65</v>
+        <v>-23.51</v>
       </c>
       <c r="L557" t="n">
-        <v>-22648.9</v>
+        <v>-23510.97</v>
       </c>
     </row>
     <row r="558">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="H561" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I561" t="n">
         <v>10.13</v>

--- a/result/全部明细.xlsx
+++ b/result/全部明细.xlsx
@@ -10424,7 +10424,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -10433,19 +10433,19 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I208" t="n">
         <v>3.95</v>
       </c>
       <c r="J208" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="K208" t="n">
-        <v>-15.7</v>
+        <v>-17.22</v>
       </c>
       <c r="L208" t="n">
-        <v>-15696.2</v>
+        <v>-17215.19</v>
       </c>
     </row>
     <row r="209">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -12561,19 +12561,19 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I252" t="n">
         <v>9.16</v>
       </c>
       <c r="J252" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="K252" t="n">
-        <v>-41.05</v>
+        <v>-41.81</v>
       </c>
       <c r="L252" t="n">
-        <v>-41048.03</v>
+        <v>-41812.23</v>
       </c>
     </row>
     <row r="253">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -12611,19 +12611,19 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I253" t="n">
         <v>12.59</v>
       </c>
       <c r="J253" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="K253" t="n">
-        <v>-30.18</v>
+        <v>-30.98</v>
       </c>
       <c r="L253" t="n">
-        <v>-30182.68</v>
+        <v>-30976.97</v>
       </c>
     </row>
     <row r="254">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -12761,19 +12761,19 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I256" t="n">
         <v>5.76</v>
       </c>
       <c r="J256" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="K256" t="n">
-        <v>-37.5</v>
+        <v>-39.41</v>
       </c>
       <c r="L256" t="n">
-        <v>-37500</v>
+        <v>-39409.72</v>
       </c>
     </row>
     <row r="257">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -13637,19 +13637,19 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I274" t="n">
         <v>41.42</v>
       </c>
       <c r="J274" t="n">
-        <v>26.27</v>
+        <v>26.28</v>
       </c>
       <c r="K274" t="n">
-        <v>-36.58</v>
+        <v>-36.55</v>
       </c>
       <c r="L274" t="n">
-        <v>-36576.53</v>
+        <v>-36552.39</v>
       </c>
     </row>
     <row r="275">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -14175,19 +14175,19 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I285" t="n">
         <v>10.64</v>
       </c>
       <c r="J285" t="n">
-        <v>7.55</v>
+        <v>7.44</v>
       </c>
       <c r="K285" t="n">
-        <v>-29.04</v>
+        <v>-30.08</v>
       </c>
       <c r="L285" t="n">
-        <v>-29041.35</v>
+        <v>-30075.19</v>
       </c>
     </row>
     <row r="286">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -15907,19 +15907,19 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I321" t="n">
         <v>21.93</v>
       </c>
       <c r="J321" t="n">
-        <v>11.42</v>
+        <v>11.52</v>
       </c>
       <c r="K321" t="n">
-        <v>-47.93</v>
+        <v>-47.47</v>
       </c>
       <c r="L321" t="n">
-        <v>-47925.22</v>
+        <v>-47469.22</v>
       </c>
     </row>
     <row r="322">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -16683,19 +16683,19 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I337" t="n">
         <v>16.39</v>
       </c>
       <c r="J337" t="n">
-        <v>9.92</v>
+        <v>9.6</v>
       </c>
       <c r="K337" t="n">
-        <v>-39.48</v>
+        <v>-41.43</v>
       </c>
       <c r="L337" t="n">
-        <v>-39475.29</v>
+        <v>-41427.7</v>
       </c>
     </row>
     <row r="338">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -16879,19 +16879,19 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I341" t="n">
         <v>11.34</v>
       </c>
       <c r="J341" t="n">
-        <v>4.64</v>
+        <v>4.4</v>
       </c>
       <c r="K341" t="n">
-        <v>-59.08</v>
+        <v>-61.2</v>
       </c>
       <c r="L341" t="n">
-        <v>-59082.89</v>
+        <v>-61199.29</v>
       </c>
     </row>
     <row r="342">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -18323,19 +18323,19 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I371" t="n">
         <v>17.35</v>
       </c>
       <c r="J371" t="n">
-        <v>12.47</v>
+        <v>11.22</v>
       </c>
       <c r="K371" t="n">
-        <v>-28.13</v>
+        <v>-35.33</v>
       </c>
       <c r="L371" t="n">
-        <v>-28126.8</v>
+        <v>-35331.41</v>
       </c>
     </row>
     <row r="372">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -18419,19 +18419,19 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I373" t="n">
         <v>27.27</v>
       </c>
       <c r="J373" t="n">
-        <v>15.22</v>
+        <v>15.04</v>
       </c>
       <c r="K373" t="n">
-        <v>-44.19</v>
+        <v>-44.85</v>
       </c>
       <c r="L373" t="n">
-        <v>-44187.75</v>
+        <v>-44847.82</v>
       </c>
     </row>
     <row r="374">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -18715,19 +18715,19 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I379" t="n">
         <v>4.34</v>
       </c>
       <c r="J379" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="K379" t="n">
-        <v>-25.58</v>
+        <v>-24.65</v>
       </c>
       <c r="L379" t="n">
-        <v>-25576.04</v>
+        <v>-24654.38</v>
       </c>
     </row>
     <row r="380">
@@ -18998,7 +18998,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -19007,19 +19007,19 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I385" t="n">
         <v>5.18</v>
       </c>
       <c r="J385" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="K385" t="n">
-        <v>-44.79</v>
+        <v>-46.72</v>
       </c>
       <c r="L385" t="n">
-        <v>-44787.64</v>
+        <v>-46718.15</v>
       </c>
     </row>
     <row r="386">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -19107,19 +19107,19 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I387" t="n">
         <v>15.63</v>
       </c>
       <c r="J387" t="n">
-        <v>10.89</v>
+        <v>10.71</v>
       </c>
       <c r="K387" t="n">
-        <v>-30.33</v>
+        <v>-31.48</v>
       </c>
       <c r="L387" t="n">
-        <v>-30326.3</v>
+        <v>-31477.93</v>
       </c>
     </row>
     <row r="388">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -20209,19 +20209,19 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I410" t="n">
         <v>13.47</v>
       </c>
       <c r="J410" t="n">
-        <v>6.94</v>
+        <v>6.79</v>
       </c>
       <c r="K410" t="n">
-        <v>-48.48</v>
+        <v>-49.59</v>
       </c>
       <c r="L410" t="n">
-        <v>-48478.1</v>
+        <v>-49591.69</v>
       </c>
     </row>
     <row r="411">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -20259,19 +20259,19 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I411" t="n">
         <v>13.58</v>
       </c>
       <c r="J411" t="n">
-        <v>8.789999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K411" t="n">
-        <v>-35.27</v>
+        <v>-36.38</v>
       </c>
       <c r="L411" t="n">
-        <v>-35272.46</v>
+        <v>-36377.03</v>
       </c>
     </row>
     <row r="412">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -20927,19 +20927,19 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I425" t="n">
         <v>16.44</v>
       </c>
       <c r="J425" t="n">
-        <v>9.75</v>
+        <v>9.56</v>
       </c>
       <c r="K425" t="n">
-        <v>-40.69</v>
+        <v>-41.85</v>
       </c>
       <c r="L425" t="n">
-        <v>-40693.43</v>
+        <v>-41849.15</v>
       </c>
     </row>
     <row r="426">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -21415,19 +21415,19 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I435" t="n">
         <v>11.59</v>
       </c>
       <c r="J435" t="n">
-        <v>7.32</v>
+        <v>7.19</v>
       </c>
       <c r="K435" t="n">
-        <v>-36.84</v>
+        <v>-37.96</v>
       </c>
       <c r="L435" t="n">
-        <v>-36842.11</v>
+        <v>-37963.76</v>
       </c>
     </row>
     <row r="436">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -22141,19 +22141,19 @@
         </is>
       </c>
       <c r="H450" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I450" t="n">
         <v>24.89</v>
       </c>
       <c r="J450" t="n">
-        <v>17.69</v>
+        <v>17.06</v>
       </c>
       <c r="K450" t="n">
-        <v>-28.93</v>
+        <v>-31.46</v>
       </c>
       <c r="L450" t="n">
-        <v>-28927.28</v>
+        <v>-31458.42</v>
       </c>
     </row>
     <row r="451">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -22913,19 +22913,19 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I466" t="n">
         <v>8.52</v>
       </c>
       <c r="J466" t="n">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="K466" t="n">
-        <v>-51.88</v>
+        <v>-52.7</v>
       </c>
       <c r="L466" t="n">
-        <v>-51877.93</v>
+        <v>-52699.53</v>
       </c>
     </row>
     <row r="467">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -22963,19 +22963,19 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I467" t="n">
         <v>7.88</v>
       </c>
       <c r="J467" t="n">
-        <v>4.37</v>
+        <v>4.22</v>
       </c>
       <c r="K467" t="n">
-        <v>-44.54</v>
+        <v>-46.45</v>
       </c>
       <c r="L467" t="n">
-        <v>-44543.15</v>
+        <v>-46446.7</v>
       </c>
     </row>
     <row r="468">
@@ -23054,7 +23054,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -23063,19 +23063,19 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I469" t="n">
         <v>12.68</v>
       </c>
       <c r="J469" t="n">
-        <v>10.97</v>
+        <v>12.12</v>
       </c>
       <c r="K469" t="n">
-        <v>-13.49</v>
+        <v>-4.42</v>
       </c>
       <c r="L469" t="n">
-        <v>-13485.8</v>
+        <v>-4416.4</v>
       </c>
     </row>
     <row r="470">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -23263,19 +23263,19 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I473" t="n">
         <v>82.72</v>
       </c>
       <c r="J473" t="n">
-        <v>61.17</v>
+        <v>61.56</v>
       </c>
       <c r="K473" t="n">
-        <v>-26.05</v>
+        <v>-25.58</v>
       </c>
       <c r="L473" t="n">
-        <v>-26051.74</v>
+        <v>-25580.27</v>
       </c>
     </row>
     <row r="474">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -23413,19 +23413,19 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I476" t="n">
         <v>31.43</v>
       </c>
       <c r="J476" t="n">
-        <v>23.13</v>
+        <v>22.99</v>
       </c>
       <c r="K476" t="n">
-        <v>-26.41</v>
+        <v>-26.85</v>
       </c>
       <c r="L476" t="n">
-        <v>-26407.89</v>
+        <v>-26853.32</v>
       </c>
     </row>
     <row r="477">
@@ -25694,7 +25694,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -25703,19 +25703,19 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I523" t="n">
         <v>37.03</v>
       </c>
       <c r="J523" t="n">
-        <v>26.58</v>
+        <v>26.47</v>
       </c>
       <c r="K523" t="n">
-        <v>-28.22</v>
+        <v>-28.52</v>
       </c>
       <c r="L523" t="n">
-        <v>-28220.36</v>
+        <v>-28517.42</v>
       </c>
     </row>
     <row r="524">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -25753,19 +25753,19 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I524" t="n">
         <v>47.26</v>
       </c>
       <c r="J524" t="n">
-        <v>25.03</v>
+        <v>24.56</v>
       </c>
       <c r="K524" t="n">
-        <v>-47.04</v>
+        <v>-48.03</v>
       </c>
       <c r="L524" t="n">
-        <v>-47037.66</v>
+        <v>-48032.16</v>
       </c>
     </row>
     <row r="525">
@@ -25794,28 +25794,28 @@
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>0940</t>
         </is>
       </c>
       <c r="H525" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I525" t="n">
         <v>127.39</v>
       </c>
       <c r="J525" t="n">
-        <v>128.71</v>
+        <v>137.3</v>
       </c>
       <c r="K525" t="n">
-        <v>1.04</v>
+        <v>7.78</v>
       </c>
       <c r="L525" t="n">
-        <v>1036.19</v>
+        <v>7779.26</v>
       </c>
     </row>
     <row r="526">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -26141,19 +26141,19 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I532" t="n">
         <v>12.76</v>
       </c>
       <c r="J532" t="n">
-        <v>9.76</v>
+        <v>9.35</v>
       </c>
       <c r="K532" t="n">
-        <v>-23.51</v>
+        <v>-26.72</v>
       </c>
       <c r="L532" t="n">
-        <v>-23510.97</v>
+        <v>-26724.14</v>
       </c>
     </row>
     <row r="533">
@@ -26332,7 +26332,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -26341,19 +26341,19 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I536" t="n">
         <v>10.13</v>
       </c>
       <c r="J536" t="n">
-        <v>7.94</v>
+        <v>7.72</v>
       </c>
       <c r="K536" t="n">
-        <v>-21.62</v>
+        <v>-23.79</v>
       </c>
       <c r="L536" t="n">
-        <v>-21618.95</v>
+        <v>-23790.72</v>
       </c>
     </row>
     <row r="537">

--- a/result/全部明细.xlsx
+++ b/result/全部明细.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L548"/>
+  <dimension ref="A1:L567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -10433,19 +10433,19 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I208" t="n">
         <v>3.95</v>
       </c>
       <c r="J208" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="K208" t="n">
-        <v>-17.22</v>
+        <v>-19.75</v>
       </c>
       <c r="L208" t="n">
-        <v>-17215.19</v>
+        <v>-19746.84</v>
       </c>
     </row>
     <row r="209">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -12561,19 +12561,19 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I252" t="n">
         <v>9.16</v>
       </c>
       <c r="J252" t="n">
-        <v>5.33</v>
+        <v>5.08</v>
       </c>
       <c r="K252" t="n">
-        <v>-41.81</v>
+        <v>-44.54</v>
       </c>
       <c r="L252" t="n">
-        <v>-41812.23</v>
+        <v>-44541.48</v>
       </c>
     </row>
     <row r="253">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -12611,19 +12611,19 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I253" t="n">
         <v>12.59</v>
       </c>
       <c r="J253" t="n">
-        <v>8.69</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K253" t="n">
-        <v>-30.98</v>
+        <v>-32.88</v>
       </c>
       <c r="L253" t="n">
-        <v>-30976.97</v>
+        <v>-32883.24</v>
       </c>
     </row>
     <row r="254">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -12761,19 +12761,19 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I256" t="n">
         <v>5.76</v>
       </c>
       <c r="J256" t="n">
-        <v>3.49</v>
+        <v>3.14</v>
       </c>
       <c r="K256" t="n">
-        <v>-39.41</v>
+        <v>-45.49</v>
       </c>
       <c r="L256" t="n">
-        <v>-39409.72</v>
+        <v>-45486.11</v>
       </c>
     </row>
     <row r="257">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -13637,19 +13637,19 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I274" t="n">
         <v>41.42</v>
       </c>
       <c r="J274" t="n">
-        <v>26.28</v>
+        <v>23.3</v>
       </c>
       <c r="K274" t="n">
-        <v>-36.55</v>
+        <v>-43.75</v>
       </c>
       <c r="L274" t="n">
-        <v>-36552.39</v>
+        <v>-43746.98</v>
       </c>
     </row>
     <row r="275">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -14175,19 +14175,19 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I285" t="n">
         <v>10.64</v>
       </c>
       <c r="J285" t="n">
-        <v>7.44</v>
+        <v>7.21</v>
       </c>
       <c r="K285" t="n">
-        <v>-30.08</v>
+        <v>-32.24</v>
       </c>
       <c r="L285" t="n">
-        <v>-30075.19</v>
+        <v>-32236.84</v>
       </c>
     </row>
     <row r="286">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -15907,19 +15907,19 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I321" t="n">
         <v>21.93</v>
       </c>
       <c r="J321" t="n">
-        <v>11.52</v>
+        <v>10.6</v>
       </c>
       <c r="K321" t="n">
-        <v>-47.47</v>
+        <v>-51.66</v>
       </c>
       <c r="L321" t="n">
-        <v>-47469.22</v>
+        <v>-51664.39</v>
       </c>
     </row>
     <row r="322">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -16683,19 +16683,19 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I337" t="n">
         <v>16.39</v>
       </c>
       <c r="J337" t="n">
-        <v>9.6</v>
+        <v>9.31</v>
       </c>
       <c r="K337" t="n">
-        <v>-41.43</v>
+        <v>-43.2</v>
       </c>
       <c r="L337" t="n">
-        <v>-41427.7</v>
+        <v>-43197.07</v>
       </c>
     </row>
     <row r="338">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -16879,19 +16879,19 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I341" t="n">
         <v>11.34</v>
       </c>
       <c r="J341" t="n">
-        <v>4.4</v>
+        <v>4.28</v>
       </c>
       <c r="K341" t="n">
-        <v>-61.2</v>
+        <v>-62.26</v>
       </c>
       <c r="L341" t="n">
-        <v>-61199.29</v>
+        <v>-62257.5</v>
       </c>
     </row>
     <row r="342">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -18323,19 +18323,19 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I371" t="n">
         <v>17.35</v>
       </c>
       <c r="J371" t="n">
-        <v>11.22</v>
+        <v>10.82</v>
       </c>
       <c r="K371" t="n">
-        <v>-35.33</v>
+        <v>-37.64</v>
       </c>
       <c r="L371" t="n">
-        <v>-35331.41</v>
+        <v>-37636.89</v>
       </c>
     </row>
     <row r="372">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -18419,19 +18419,19 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I373" t="n">
         <v>27.27</v>
       </c>
       <c r="J373" t="n">
-        <v>15.04</v>
+        <v>14.16</v>
       </c>
       <c r="K373" t="n">
-        <v>-44.85</v>
+        <v>-48.07</v>
       </c>
       <c r="L373" t="n">
-        <v>-44847.82</v>
+        <v>-48074.81</v>
       </c>
     </row>
     <row r="374">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -18715,7 +18715,7 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I379" t="n">
         <v>4.34</v>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -19007,19 +19007,19 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I385" t="n">
         <v>5.18</v>
       </c>
       <c r="J385" t="n">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="K385" t="n">
-        <v>-46.72</v>
+        <v>-49.42</v>
       </c>
       <c r="L385" t="n">
-        <v>-46718.15</v>
+        <v>-49420.85</v>
       </c>
     </row>
     <row r="386">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -19107,19 +19107,19 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="I387" t="n">
         <v>15.63</v>
       </c>
       <c r="J387" t="n">
-        <v>10.71</v>
+        <v>12</v>
       </c>
       <c r="K387" t="n">
-        <v>-31.48</v>
+        <v>-23.22</v>
       </c>
       <c r="L387" t="n">
-        <v>-31477.93</v>
+        <v>-23224.57</v>
       </c>
     </row>
     <row r="388">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -20209,19 +20209,19 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I410" t="n">
         <v>13.47</v>
       </c>
       <c r="J410" t="n">
-        <v>6.79</v>
+        <v>6.25</v>
       </c>
       <c r="K410" t="n">
-        <v>-49.59</v>
+        <v>-53.6</v>
       </c>
       <c r="L410" t="n">
-        <v>-49591.69</v>
+        <v>-53600.59</v>
       </c>
     </row>
     <row r="411">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -20259,19 +20259,19 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="I411" t="n">
         <v>13.58</v>
       </c>
       <c r="J411" t="n">
-        <v>8.640000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K411" t="n">
-        <v>-36.38</v>
+        <v>-39.47</v>
       </c>
       <c r="L411" t="n">
-        <v>-36377.03</v>
+        <v>-39469.81</v>
       </c>
     </row>
     <row r="412">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -20927,19 +20927,19 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I425" t="n">
         <v>16.44</v>
       </c>
       <c r="J425" t="n">
-        <v>9.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K425" t="n">
-        <v>-41.85</v>
+        <v>-44.04</v>
       </c>
       <c r="L425" t="n">
-        <v>-41849.15</v>
+        <v>-44038.93</v>
       </c>
     </row>
     <row r="426">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -21415,19 +21415,19 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I435" t="n">
         <v>11.59</v>
       </c>
       <c r="J435" t="n">
-        <v>7.19</v>
+        <v>7.06</v>
       </c>
       <c r="K435" t="n">
-        <v>-37.96</v>
+        <v>-39.09</v>
       </c>
       <c r="L435" t="n">
-        <v>-37963.76</v>
+        <v>-39085.42</v>
       </c>
     </row>
     <row r="436">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -22141,19 +22141,19 @@
         </is>
       </c>
       <c r="H450" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I450" t="n">
         <v>24.89</v>
       </c>
       <c r="J450" t="n">
-        <v>17.06</v>
+        <v>15.73</v>
       </c>
       <c r="K450" t="n">
-        <v>-31.46</v>
+        <v>-36.8</v>
       </c>
       <c r="L450" t="n">
-        <v>-31458.42</v>
+        <v>-36801.93</v>
       </c>
     </row>
     <row r="451">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -22913,19 +22913,19 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I466" t="n">
         <v>8.52</v>
       </c>
       <c r="J466" t="n">
-        <v>4.03</v>
+        <v>3.78</v>
       </c>
       <c r="K466" t="n">
-        <v>-52.7</v>
+        <v>-55.63</v>
       </c>
       <c r="L466" t="n">
-        <v>-52699.53</v>
+        <v>-55633.8</v>
       </c>
     </row>
     <row r="467">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -22963,19 +22963,19 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I467" t="n">
         <v>7.88</v>
       </c>
       <c r="J467" t="n">
-        <v>4.22</v>
+        <v>4.04</v>
       </c>
       <c r="K467" t="n">
-        <v>-46.45</v>
+        <v>-48.73</v>
       </c>
       <c r="L467" t="n">
-        <v>-46446.7</v>
+        <v>-48730.96</v>
       </c>
     </row>
     <row r="468">
@@ -23054,7 +23054,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -23063,19 +23063,19 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I469" t="n">
         <v>12.68</v>
       </c>
       <c r="J469" t="n">
-        <v>12.12</v>
+        <v>12.55</v>
       </c>
       <c r="K469" t="n">
-        <v>-4.42</v>
+        <v>-1.03</v>
       </c>
       <c r="L469" t="n">
-        <v>-4416.4</v>
+        <v>-1025.24</v>
       </c>
     </row>
     <row r="470">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -23263,19 +23263,19 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I473" t="n">
         <v>82.72</v>
       </c>
       <c r="J473" t="n">
-        <v>61.56</v>
+        <v>58.01</v>
       </c>
       <c r="K473" t="n">
-        <v>-25.58</v>
+        <v>-29.87</v>
       </c>
       <c r="L473" t="n">
-        <v>-25580.27</v>
+        <v>-29871.86</v>
       </c>
     </row>
     <row r="474">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -23413,19 +23413,19 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I476" t="n">
         <v>31.43</v>
       </c>
       <c r="J476" t="n">
-        <v>22.99</v>
+        <v>22.78</v>
       </c>
       <c r="K476" t="n">
-        <v>-26.85</v>
+        <v>-27.52</v>
       </c>
       <c r="L476" t="n">
-        <v>-26853.32</v>
+        <v>-27521.48</v>
       </c>
     </row>
     <row r="477">
@@ -25694,7 +25694,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -25703,19 +25703,19 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I523" t="n">
         <v>37.03</v>
       </c>
       <c r="J523" t="n">
-        <v>26.47</v>
+        <v>27.04</v>
       </c>
       <c r="K523" t="n">
-        <v>-28.52</v>
+        <v>-26.98</v>
       </c>
       <c r="L523" t="n">
-        <v>-28517.42</v>
+        <v>-26978.13</v>
       </c>
     </row>
     <row r="524">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -25753,19 +25753,19 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I524" t="n">
         <v>47.26</v>
       </c>
       <c r="J524" t="n">
-        <v>24.56</v>
+        <v>23.45</v>
       </c>
       <c r="K524" t="n">
-        <v>-48.03</v>
+        <v>-50.38</v>
       </c>
       <c r="L524" t="n">
-        <v>-48032.16</v>
+        <v>-50380.87</v>
       </c>
     </row>
     <row r="525">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -26141,19 +26141,19 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I532" t="n">
         <v>12.76</v>
       </c>
       <c r="J532" t="n">
-        <v>9.35</v>
+        <v>8.91</v>
       </c>
       <c r="K532" t="n">
-        <v>-26.72</v>
+        <v>-30.17</v>
       </c>
       <c r="L532" t="n">
-        <v>-26724.14</v>
+        <v>-30172.41</v>
       </c>
     </row>
     <row r="533">
@@ -26332,7 +26332,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -26341,19 +26341,19 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I536" t="n">
         <v>10.13</v>
       </c>
       <c r="J536" t="n">
-        <v>7.72</v>
+        <v>7.5</v>
       </c>
       <c r="K536" t="n">
-        <v>-23.79</v>
+        <v>-25.96</v>
       </c>
       <c r="L536" t="n">
-        <v>-23790.72</v>
+        <v>-25962.49</v>
       </c>
     </row>
     <row r="537">
@@ -26934,6 +26934,948 @@
       </c>
       <c r="L548" t="n">
         <v>4454.02</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>SZ301132</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>满坤科技</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>1</v>
+      </c>
+      <c r="I549" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="J549" t="n">
+        <v>54</v>
+      </c>
+      <c r="K549" t="n">
+        <v>-3.17</v>
+      </c>
+      <c r="L549" t="n">
+        <v>-3173.75</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>SZ002631</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>德尔未来</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>2</v>
+      </c>
+      <c r="I550" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="J550" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="K550" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L550" t="n">
+        <v>1952.72</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>SZ001359</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>平安电工</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>-19.18</v>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>1</v>
+      </c>
+      <c r="I551" t="n">
+        <v>117.53</v>
+      </c>
+      <c r="J551" t="n">
+        <v>126.56</v>
+      </c>
+      <c r="K551" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="L551" t="n">
+        <v>7683.14</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>SZ002068</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>黑猫股份</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>3</v>
+      </c>
+      <c r="I552" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="J552" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="K552" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="L552" t="n">
+        <v>15445.86</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>SZ002608</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>江苏国信</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>24</v>
+      </c>
+      <c r="I553" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="J553" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="K553" t="n">
+        <v>-32.33</v>
+      </c>
+      <c r="L553" t="n">
+        <v>-32333.01</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>SZ300184</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr"/>
+      <c r="H554" t="n">
+        <v>6</v>
+      </c>
+      <c r="I554" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="J554" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="K554" t="n">
+        <v>-13.96</v>
+      </c>
+      <c r="L554" t="n">
+        <v>-13959.8</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>SZ301150</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>中一科技</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>6</v>
+      </c>
+      <c r="I555" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="J555" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="K555" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="L555" t="n">
+        <v>6053.57</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>SZ002515</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>金字火腿</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>0935</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>5</v>
+      </c>
+      <c r="I556" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="J556" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="K556" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="L556" t="n">
+        <v>6118.14</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>SZ002971</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>和远气体</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>0935</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>1</v>
+      </c>
+      <c r="I557" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="J557" t="n">
+        <v>59.97</v>
+      </c>
+      <c r="K557" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="L557" t="n">
+        <v>7165.83</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>SZ300706</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>阿石创</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>3</v>
+      </c>
+      <c r="I558" t="n">
+        <v>71.61</v>
+      </c>
+      <c r="J558" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="K558" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="L558" t="n">
+        <v>6018.71</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>SH600500</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>中化国际</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>1</v>
+      </c>
+      <c r="I559" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="J559" t="n">
+        <v>9</v>
+      </c>
+      <c r="K559" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L559" t="n">
+        <v>10294.12</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>SZ002125</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>湘潭电化</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>5</v>
+      </c>
+      <c r="I560" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="J560" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="K560" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="L560" t="n">
+        <v>11742.01</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>SZ002645</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>华宏科技</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>-13.82</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>3</v>
+      </c>
+      <c r="I561" t="n">
+        <v>31.11</v>
+      </c>
+      <c r="J561" t="n">
+        <v>33.53</v>
+      </c>
+      <c r="K561" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="L561" t="n">
+        <v>7778.85</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>SZ000608</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>阳光股份</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>1120</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>1</v>
+      </c>
+      <c r="I562" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="J562" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="K562" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="L562" t="n">
+        <v>7890.22</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>SZ002138</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>顺络电子</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>1</v>
+      </c>
+      <c r="I563" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="J563" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="K563" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="L563" t="n">
+        <v>8180.21</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>SZ300319</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>麦捷科技</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr"/>
+      <c r="H564" t="n">
+        <v>7</v>
+      </c>
+      <c r="I564" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J564" t="n">
+        <v>22.07</v>
+      </c>
+      <c r="K564" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="L564" t="n">
+        <v>23296.09</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>SZ002851</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>麦格米特</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>14</v>
+      </c>
+      <c r="I565" t="n">
+        <v>156.4</v>
+      </c>
+      <c r="J565" t="n">
+        <v>169.07</v>
+      </c>
+      <c r="K565" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L565" t="n">
+        <v>8101.02</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>SZ300747</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>锐科激光</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>23</v>
+      </c>
+      <c r="I566" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="J566" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="K566" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="L566" t="n">
+        <v>13730.79</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>SZ003004</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>声迅股份</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>21</v>
+      </c>
+      <c r="I567" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="J567" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="K567" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="L567" t="n">
+        <v>6886.66</v>
       </c>
     </row>
   </sheetData>

--- a/result/全部明细.xlsx
+++ b/result/全部明细.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L567"/>
+  <dimension ref="A1:L604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -10433,19 +10433,19 @@
         </is>
       </c>
       <c r="H208" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="I208" t="n">
         <v>3.95</v>
       </c>
       <c r="J208" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="K208" t="n">
-        <v>-19.75</v>
+        <v>-20.76</v>
       </c>
       <c r="L208" t="n">
-        <v>-19746.84</v>
+        <v>-20759.49</v>
       </c>
     </row>
     <row r="209">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -12561,19 +12561,19 @@
         </is>
       </c>
       <c r="H252" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I252" t="n">
         <v>9.16</v>
       </c>
       <c r="J252" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="K252" t="n">
-        <v>-44.54</v>
+        <v>-44.65</v>
       </c>
       <c r="L252" t="n">
-        <v>-44541.48</v>
+        <v>-44650.66</v>
       </c>
     </row>
     <row r="253">
@@ -12602,7 +12602,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -12611,19 +12611,19 @@
         </is>
       </c>
       <c r="H253" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I253" t="n">
         <v>12.59</v>
       </c>
       <c r="J253" t="n">
-        <v>8.449999999999999</v>
+        <v>6.94</v>
       </c>
       <c r="K253" t="n">
-        <v>-32.88</v>
+        <v>-44.88</v>
       </c>
       <c r="L253" t="n">
-        <v>-32883.24</v>
+        <v>-44876.89</v>
       </c>
     </row>
     <row r="254">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -12761,19 +12761,19 @@
         </is>
       </c>
       <c r="H256" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I256" t="n">
         <v>5.76</v>
       </c>
       <c r="J256" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="K256" t="n">
-        <v>-45.49</v>
+        <v>-50.52</v>
       </c>
       <c r="L256" t="n">
-        <v>-45486.11</v>
+        <v>-50520.83</v>
       </c>
     </row>
     <row r="257">
@@ -13628,7 +13628,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -13637,19 +13637,19 @@
         </is>
       </c>
       <c r="H274" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I274" t="n">
         <v>41.42</v>
       </c>
       <c r="J274" t="n">
-        <v>23.3</v>
+        <v>23.82</v>
       </c>
       <c r="K274" t="n">
-        <v>-43.75</v>
+        <v>-42.49</v>
       </c>
       <c r="L274" t="n">
-        <v>-43746.98</v>
+        <v>-42491.55</v>
       </c>
     </row>
     <row r="275">
@@ -14166,7 +14166,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -14175,19 +14175,19 @@
         </is>
       </c>
       <c r="H285" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I285" t="n">
         <v>10.64</v>
       </c>
       <c r="J285" t="n">
-        <v>7.21</v>
+        <v>7.23</v>
       </c>
       <c r="K285" t="n">
-        <v>-32.24</v>
+        <v>-32.05</v>
       </c>
       <c r="L285" t="n">
-        <v>-32236.84</v>
+        <v>-32048.87</v>
       </c>
     </row>
     <row r="286">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -15907,19 +15907,19 @@
         </is>
       </c>
       <c r="H321" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I321" t="n">
         <v>21.93</v>
       </c>
       <c r="J321" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="K321" t="n">
-        <v>-51.66</v>
+        <v>-53.03</v>
       </c>
       <c r="L321" t="n">
-        <v>-51664.39</v>
+        <v>-53032.38</v>
       </c>
     </row>
     <row r="322">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -16683,19 +16683,19 @@
         </is>
       </c>
       <c r="H337" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I337" t="n">
         <v>16.39</v>
       </c>
       <c r="J337" t="n">
-        <v>9.31</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K337" t="n">
-        <v>-43.2</v>
+        <v>-43.87</v>
       </c>
       <c r="L337" t="n">
-        <v>-43197.07</v>
+        <v>-43868.21</v>
       </c>
     </row>
     <row r="338">
@@ -16870,7 +16870,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -16879,7 +16879,7 @@
         </is>
       </c>
       <c r="H341" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I341" t="n">
         <v>11.34</v>
@@ -18314,7 +18314,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -18323,19 +18323,19 @@
         </is>
       </c>
       <c r="H371" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I371" t="n">
         <v>17.35</v>
       </c>
       <c r="J371" t="n">
-        <v>10.82</v>
+        <v>10.84</v>
       </c>
       <c r="K371" t="n">
-        <v>-37.64</v>
+        <v>-37.52</v>
       </c>
       <c r="L371" t="n">
-        <v>-37636.89</v>
+        <v>-37521.61</v>
       </c>
     </row>
     <row r="372">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -18419,19 +18419,19 @@
         </is>
       </c>
       <c r="H373" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I373" t="n">
         <v>27.27</v>
       </c>
       <c r="J373" t="n">
-        <v>14.16</v>
+        <v>14.05</v>
       </c>
       <c r="K373" t="n">
-        <v>-48.07</v>
+        <v>-48.48</v>
       </c>
       <c r="L373" t="n">
-        <v>-48074.81</v>
+        <v>-48478.18</v>
       </c>
     </row>
     <row r="374">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -18715,19 +18715,19 @@
         </is>
       </c>
       <c r="H379" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I379" t="n">
         <v>4.34</v>
       </c>
       <c r="J379" t="n">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="K379" t="n">
-        <v>-24.65</v>
+        <v>-23.73</v>
       </c>
       <c r="L379" t="n">
-        <v>-24654.38</v>
+        <v>-23732.72</v>
       </c>
     </row>
     <row r="380">
@@ -18998,7 +18998,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
@@ -19007,19 +19007,19 @@
         </is>
       </c>
       <c r="H385" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I385" t="n">
         <v>5.18</v>
       </c>
       <c r="J385" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="K385" t="n">
-        <v>-49.42</v>
+        <v>-49.23</v>
       </c>
       <c r="L385" t="n">
-        <v>-49420.85</v>
+        <v>-49227.8</v>
       </c>
     </row>
     <row r="386">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -19107,19 +19107,19 @@
         </is>
       </c>
       <c r="H387" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="I387" t="n">
         <v>15.63</v>
       </c>
       <c r="J387" t="n">
-        <v>12</v>
+        <v>11.44</v>
       </c>
       <c r="K387" t="n">
-        <v>-23.22</v>
+        <v>-26.81</v>
       </c>
       <c r="L387" t="n">
-        <v>-23224.57</v>
+        <v>-26807.42</v>
       </c>
     </row>
     <row r="388">
@@ -20200,7 +20200,7 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
@@ -20209,19 +20209,19 @@
         </is>
       </c>
       <c r="H410" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I410" t="n">
         <v>13.47</v>
       </c>
       <c r="J410" t="n">
-        <v>6.25</v>
+        <v>6.18</v>
       </c>
       <c r="K410" t="n">
-        <v>-53.6</v>
+        <v>-54.12</v>
       </c>
       <c r="L410" t="n">
-        <v>-53600.59</v>
+        <v>-54120.27</v>
       </c>
     </row>
     <row r="411">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
@@ -20259,19 +20259,19 @@
         </is>
       </c>
       <c r="H411" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="I411" t="n">
         <v>13.58</v>
       </c>
       <c r="J411" t="n">
-        <v>8.220000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="K411" t="n">
-        <v>-39.47</v>
+        <v>-39.99</v>
       </c>
       <c r="L411" t="n">
-        <v>-39469.81</v>
+        <v>-39985.27</v>
       </c>
     </row>
     <row r="412">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
@@ -20927,19 +20927,19 @@
         </is>
       </c>
       <c r="H425" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I425" t="n">
         <v>16.44</v>
       </c>
       <c r="J425" t="n">
-        <v>9.199999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K425" t="n">
-        <v>-44.04</v>
+        <v>-44.4</v>
       </c>
       <c r="L425" t="n">
-        <v>-44038.93</v>
+        <v>-44403.89</v>
       </c>
     </row>
     <row r="426">
@@ -21406,7 +21406,7 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
@@ -21415,19 +21415,19 @@
         </is>
       </c>
       <c r="H435" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I435" t="n">
         <v>11.59</v>
       </c>
       <c r="J435" t="n">
-        <v>7.06</v>
+        <v>6.92</v>
       </c>
       <c r="K435" t="n">
-        <v>-39.09</v>
+        <v>-40.29</v>
       </c>
       <c r="L435" t="n">
-        <v>-39085.42</v>
+        <v>-40293.36</v>
       </c>
     </row>
     <row r="436">
@@ -22132,7 +22132,7 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
@@ -22141,19 +22141,19 @@
         </is>
       </c>
       <c r="H450" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I450" t="n">
         <v>24.89</v>
       </c>
       <c r="J450" t="n">
-        <v>15.73</v>
+        <v>15.65</v>
       </c>
       <c r="K450" t="n">
-        <v>-36.8</v>
+        <v>-37.12</v>
       </c>
       <c r="L450" t="n">
-        <v>-36801.93</v>
+        <v>-37123.34</v>
       </c>
     </row>
     <row r="451">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -22913,19 +22913,19 @@
         </is>
       </c>
       <c r="H466" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I466" t="n">
         <v>8.52</v>
       </c>
       <c r="J466" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="K466" t="n">
-        <v>-55.63</v>
+        <v>-55.16</v>
       </c>
       <c r="L466" t="n">
-        <v>-55633.8</v>
+        <v>-55164.32</v>
       </c>
     </row>
     <row r="467">
@@ -22954,7 +22954,7 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -22963,19 +22963,19 @@
         </is>
       </c>
       <c r="H467" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="I467" t="n">
         <v>7.88</v>
       </c>
       <c r="J467" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="K467" t="n">
-        <v>-48.73</v>
+        <v>-48.6</v>
       </c>
       <c r="L467" t="n">
-        <v>-48730.96</v>
+        <v>-48604.06</v>
       </c>
     </row>
     <row r="468">
@@ -23054,7 +23054,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -23063,19 +23063,19 @@
         </is>
       </c>
       <c r="H469" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I469" t="n">
         <v>12.68</v>
       </c>
       <c r="J469" t="n">
-        <v>12.55</v>
+        <v>12.76</v>
       </c>
       <c r="K469" t="n">
-        <v>-1.03</v>
+        <v>0.63</v>
       </c>
       <c r="L469" t="n">
-        <v>-1025.24</v>
+        <v>630.91</v>
       </c>
     </row>
     <row r="470">
@@ -23254,7 +23254,7 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
@@ -23263,19 +23263,19 @@
         </is>
       </c>
       <c r="H473" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I473" t="n">
         <v>82.72</v>
       </c>
       <c r="J473" t="n">
-        <v>58.01</v>
+        <v>61.43</v>
       </c>
       <c r="K473" t="n">
-        <v>-29.87</v>
+        <v>-25.74</v>
       </c>
       <c r="L473" t="n">
-        <v>-29871.86</v>
+        <v>-25737.43</v>
       </c>
     </row>
     <row r="474">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
@@ -23413,19 +23413,19 @@
         </is>
       </c>
       <c r="H476" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="I476" t="n">
         <v>31.43</v>
       </c>
       <c r="J476" t="n">
-        <v>22.78</v>
+        <v>22.84</v>
       </c>
       <c r="K476" t="n">
-        <v>-27.52</v>
+        <v>-27.33</v>
       </c>
       <c r="L476" t="n">
-        <v>-27521.48</v>
+        <v>-27330.58</v>
       </c>
     </row>
     <row r="477">
@@ -25694,7 +25694,7 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -25703,19 +25703,19 @@
         </is>
       </c>
       <c r="H523" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I523" t="n">
         <v>37.03</v>
       </c>
       <c r="J523" t="n">
-        <v>27.04</v>
+        <v>26.82</v>
       </c>
       <c r="K523" t="n">
-        <v>-26.98</v>
+        <v>-27.57</v>
       </c>
       <c r="L523" t="n">
-        <v>-26978.13</v>
+        <v>-27572.24</v>
       </c>
     </row>
     <row r="524">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -25753,19 +25753,19 @@
         </is>
       </c>
       <c r="H524" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="I524" t="n">
         <v>47.26</v>
       </c>
       <c r="J524" t="n">
-        <v>23.45</v>
+        <v>24.93</v>
       </c>
       <c r="K524" t="n">
-        <v>-50.38</v>
+        <v>-47.25</v>
       </c>
       <c r="L524" t="n">
-        <v>-50380.87</v>
+        <v>-47249.26</v>
       </c>
     </row>
     <row r="525">
@@ -26132,7 +26132,7 @@
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -26141,19 +26141,19 @@
         </is>
       </c>
       <c r="H532" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I532" t="n">
         <v>12.76</v>
       </c>
       <c r="J532" t="n">
-        <v>8.91</v>
+        <v>8.75</v>
       </c>
       <c r="K532" t="n">
-        <v>-30.17</v>
+        <v>-31.43</v>
       </c>
       <c r="L532" t="n">
-        <v>-30172.41</v>
+        <v>-31426.33</v>
       </c>
     </row>
     <row r="533">
@@ -26332,7 +26332,7 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -26341,19 +26341,19 @@
         </is>
       </c>
       <c r="H536" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I536" t="n">
         <v>10.13</v>
       </c>
       <c r="J536" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="K536" t="n">
-        <v>-25.96</v>
+        <v>-21.03</v>
       </c>
       <c r="L536" t="n">
-        <v>-25962.49</v>
+        <v>-21026.65</v>
       </c>
     </row>
     <row r="537">
@@ -26939,12 +26939,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>SZ301132</t>
+          <t>SH603010</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>满坤科技</t>
+          <t>万盛股份</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -26953,66 +26953,66 @@
         </is>
       </c>
       <c r="D549" t="n">
-        <v>1.88</v>
+        <v>6.57</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>0935</t>
         </is>
       </c>
       <c r="H549" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I549" t="n">
-        <v>55.77</v>
+        <v>16.55</v>
       </c>
       <c r="J549" t="n">
-        <v>54</v>
+        <v>18.1</v>
       </c>
       <c r="K549" t="n">
-        <v>-3.17</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L549" t="n">
-        <v>-3173.75</v>
+        <v>9365.559999999999</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>SZ002631</t>
+          <t>SH603281</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>德尔未来</t>
+          <t>江瀚新材</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>强势</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>8.23</v>
+        <v>3</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -27021,30 +27021,30 @@
         </is>
       </c>
       <c r="H550" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I550" t="n">
-        <v>9.73</v>
+        <v>41.92</v>
       </c>
       <c r="J550" t="n">
-        <v>9.92</v>
+        <v>40.38</v>
       </c>
       <c r="K550" t="n">
-        <v>1.95</v>
+        <v>-3.67</v>
       </c>
       <c r="L550" t="n">
-        <v>1952.72</v>
+        <v>-3673.66</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>SZ001359</t>
+          <t>SZ301132</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>平安电工</t>
+          <t>满坤科技</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -27053,48 +27053,48 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>-19.18</v>
+        <v>1.88</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="H551" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I551" t="n">
-        <v>117.53</v>
+        <v>55.77</v>
       </c>
       <c r="J551" t="n">
-        <v>126.56</v>
+        <v>52.54</v>
       </c>
       <c r="K551" t="n">
-        <v>7.68</v>
+        <v>-5.79</v>
       </c>
       <c r="L551" t="n">
-        <v>7683.14</v>
+        <v>-5791.64</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>SZ002068</t>
+          <t>SZ002631</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>黑猫股份</t>
+          <t>德尔未来</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -27103,16 +27103,16 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>9.220000000000001</v>
+        <v>8.23</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -27121,30 +27121,30 @@
         </is>
       </c>
       <c r="H552" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I552" t="n">
-        <v>12.56</v>
+        <v>9.73</v>
       </c>
       <c r="J552" t="n">
-        <v>14.5</v>
+        <v>11.29</v>
       </c>
       <c r="K552" t="n">
-        <v>15.45</v>
+        <v>16.03</v>
       </c>
       <c r="L552" t="n">
-        <v>15445.86</v>
+        <v>16032.89</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>SZ002608</t>
+          <t>SH688671</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>江苏国信</t>
+          <t>碧兴物联</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -27153,48 +27153,48 @@
         </is>
       </c>
       <c r="D553" t="n">
-        <v>2.08</v>
+        <v>1.56</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="H553" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I553" t="n">
-        <v>10.33</v>
+        <v>31.26</v>
       </c>
       <c r="J553" t="n">
-        <v>6.99</v>
+        <v>33.5</v>
       </c>
       <c r="K553" t="n">
-        <v>-32.33</v>
+        <v>7.17</v>
       </c>
       <c r="L553" t="n">
-        <v>-32333.01</v>
+        <v>7165.71</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>SZ300184</t>
+          <t>SZ002068</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>力源信息</t>
+          <t>黑猫股份</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -27203,44 +27203,48 @@
         </is>
       </c>
       <c r="D554" t="n">
-        <v>8.039999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
-        </is>
-      </c>
-      <c r="G554" t="inlineStr"/>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
       <c r="H554" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I554" t="n">
-        <v>18.41</v>
+        <v>12.56</v>
       </c>
       <c r="J554" t="n">
-        <v>15.84</v>
+        <v>14.94</v>
       </c>
       <c r="K554" t="n">
-        <v>-13.96</v>
+        <v>18.95</v>
       </c>
       <c r="L554" t="n">
-        <v>-13959.8</v>
+        <v>18949.04</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>SZ301150</t>
+          <t>SZ000691</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>中一科技</t>
+          <t>亚太实业</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -27249,7 +27253,7 @@
         </is>
       </c>
       <c r="D555" t="n">
-        <v>-8.640000000000001</v>
+        <v>5.95</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
@@ -27263,34 +27267,34 @@
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>0935</t>
         </is>
       </c>
       <c r="H555" t="n">
         <v>6</v>
       </c>
       <c r="I555" t="n">
-        <v>64.59</v>
+        <v>12.28</v>
       </c>
       <c r="J555" t="n">
-        <v>68.5</v>
+        <v>13.35</v>
       </c>
       <c r="K555" t="n">
-        <v>6.05</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L555" t="n">
-        <v>6053.57</v>
+        <v>8713.360000000001</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>SZ002515</t>
+          <t>SZ001359</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>金字火腿</t>
+          <t>平安电工</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -27299,48 +27303,48 @@
         </is>
       </c>
       <c r="D556" t="n">
-        <v>4.06</v>
+        <v>-19.18</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>0935</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H556" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I556" t="n">
-        <v>9.48</v>
+        <v>117.53</v>
       </c>
       <c r="J556" t="n">
-        <v>10.06</v>
+        <v>126.56</v>
       </c>
       <c r="K556" t="n">
-        <v>6.12</v>
+        <v>7.68</v>
       </c>
       <c r="L556" t="n">
-        <v>6118.14</v>
+        <v>7683.14</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>SZ002971</t>
+          <t>SZ002768</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>和远气体</t>
+          <t>国恩股份</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -27349,98 +27353,94 @@
         </is>
       </c>
       <c r="D557" t="n">
-        <v>-3.57</v>
+        <v>-29.96</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>0935</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="H557" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I557" t="n">
-        <v>55.96</v>
+        <v>55.03</v>
       </c>
       <c r="J557" t="n">
-        <v>59.97</v>
+        <v>52.03</v>
       </c>
       <c r="K557" t="n">
-        <v>7.17</v>
+        <v>-5.45</v>
       </c>
       <c r="L557" t="n">
-        <v>7165.83</v>
+        <v>-5451.57</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>SZ300706</t>
+          <t>SZ300951</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>阿石创</t>
+          <t>博硕科技</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>强势</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>5.49</v>
+        <v>15.9</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr"/>
       <c r="H558" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I558" t="n">
-        <v>71.61</v>
+        <v>57.52</v>
       </c>
       <c r="J558" t="n">
-        <v>75.92</v>
+        <v>49.08</v>
       </c>
       <c r="K558" t="n">
-        <v>6.02</v>
+        <v>-14.67</v>
       </c>
       <c r="L558" t="n">
-        <v>6018.71</v>
+        <v>-14673.16</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>SH600500</t>
+          <t>SH603991</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>中化国际</t>
+          <t>领先股份</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -27449,48 +27449,48 @@
         </is>
       </c>
       <c r="D559" t="n">
-        <v>2.9</v>
+        <v>5.09</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>0930</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="H559" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I559" t="n">
-        <v>8.16</v>
+        <v>136.29</v>
       </c>
       <c r="J559" t="n">
-        <v>9</v>
+        <v>141.15</v>
       </c>
       <c r="K559" t="n">
-        <v>10.29</v>
+        <v>3.57</v>
       </c>
       <c r="L559" t="n">
-        <v>10294.12</v>
+        <v>3565.93</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>SZ002125</t>
+          <t>SZ300558</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>湘潭电化</t>
+          <t>贝达药业</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -27499,48 +27499,48 @@
         </is>
       </c>
       <c r="D560" t="n">
-        <v>-3.41</v>
+        <v>2.97</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>0930</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="H560" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I560" t="n">
-        <v>18.14</v>
+        <v>55.11</v>
       </c>
       <c r="J560" t="n">
-        <v>20.27</v>
+        <v>58.48</v>
       </c>
       <c r="K560" t="n">
-        <v>11.74</v>
+        <v>6.12</v>
       </c>
       <c r="L560" t="n">
-        <v>11742.01</v>
+        <v>6115.04</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>SZ002645</t>
+          <t>SZ301150</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>华宏科技</t>
+          <t>中一科技</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -27549,48 +27549,48 @@
         </is>
       </c>
       <c r="D561" t="n">
-        <v>-13.82</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>0945</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="H561" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I561" t="n">
-        <v>31.11</v>
+        <v>64.59</v>
       </c>
       <c r="J561" t="n">
-        <v>33.53</v>
+        <v>68.5</v>
       </c>
       <c r="K561" t="n">
-        <v>7.78</v>
+        <v>6.05</v>
       </c>
       <c r="L561" t="n">
-        <v>7778.85</v>
+        <v>6053.57</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>SZ000608</t>
+          <t>SH603020</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>阳光股份</t>
+          <t>XD爱普股</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
@@ -27599,144 +27599,148 @@
         </is>
       </c>
       <c r="D562" t="n">
-        <v>5.62</v>
+        <v>0.65</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="H562" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I562" t="n">
-        <v>5.83</v>
+        <v>13.98</v>
       </c>
       <c r="J562" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="K562" t="n">
         <v>6.29</v>
       </c>
-      <c r="K562" t="n">
-        <v>7.89</v>
-      </c>
       <c r="L562" t="n">
-        <v>7890.22</v>
+        <v>6294.71</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>SZ002138</t>
+          <t>SZ300031</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>顺络电子</t>
+          <t>宝通科技</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>强势</t>
+          <t>趋势</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>1.78</v>
+        <v>9.17</v>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="H563" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I563" t="n">
-        <v>56.6</v>
+        <v>30.72</v>
       </c>
       <c r="J563" t="n">
-        <v>61.23</v>
+        <v>28.49</v>
       </c>
       <c r="K563" t="n">
-        <v>8.18</v>
+        <v>-7.26</v>
       </c>
       <c r="L563" t="n">
-        <v>8180.21</v>
+        <v>-7259.11</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>SZ300319</t>
+          <t>SZ002972</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>麦捷科技</t>
+          <t>科安达</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>强势</t>
         </is>
       </c>
       <c r="D564" t="n">
-        <v>9.550000000000001</v>
+        <v>4.11</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G564" t="inlineStr"/>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
       <c r="H564" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I564" t="n">
-        <v>17.9</v>
+        <v>16.45</v>
       </c>
       <c r="J564" t="n">
-        <v>22.07</v>
+        <v>17.45</v>
       </c>
       <c r="K564" t="n">
-        <v>23.3</v>
+        <v>6.08</v>
       </c>
       <c r="L564" t="n">
-        <v>23296.09</v>
+        <v>6079.03</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>SZ002851</t>
+          <t>SZ002515</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>麦格米特</t>
+          <t>金字火腿</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
@@ -27745,98 +27749,98 @@
         </is>
       </c>
       <c r="D565" t="n">
-        <v>5.71</v>
+        <v>4.06</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>0930</t>
+          <t>0935</t>
         </is>
       </c>
       <c r="H565" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I565" t="n">
-        <v>156.4</v>
+        <v>9.48</v>
       </c>
       <c r="J565" t="n">
-        <v>169.07</v>
+        <v>10.06</v>
       </c>
       <c r="K565" t="n">
-        <v>8.1</v>
+        <v>6.12</v>
       </c>
       <c r="L565" t="n">
-        <v>8101.02</v>
+        <v>6118.14</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>SZ300747</t>
+          <t>SZ002971</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>锐科激光</t>
+          <t>和远气体</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>趋势</t>
+          <t>强势</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>18.51</v>
+        <v>-3.57</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>0935</t>
         </is>
       </c>
       <c r="H566" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I566" t="n">
-        <v>48.14</v>
+        <v>55.96</v>
       </c>
       <c r="J566" t="n">
-        <v>54.75</v>
+        <v>59.97</v>
       </c>
       <c r="K566" t="n">
-        <v>13.73</v>
+        <v>7.17</v>
       </c>
       <c r="L566" t="n">
-        <v>13730.79</v>
+        <v>7165.83</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>SZ003004</t>
+          <t>SZ301029</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>声迅股份</t>
+          <t>怡合达</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -27845,37 +27849,1855 @@
         </is>
       </c>
       <c r="D567" t="n">
-        <v>6.12</v>
+        <v>2.76</v>
       </c>
       <c r="E567" t="inlineStr">
         <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>15</v>
+      </c>
+      <c r="I567" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="J567" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="K567" t="n">
+        <v>-15.98</v>
+      </c>
+      <c r="L567" t="n">
+        <v>-15975.04</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>SZ301323</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>新莱福</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>15</v>
+      </c>
+      <c r="I568" t="n">
+        <v>108.01</v>
+      </c>
+      <c r="J568" t="n">
+        <v>81.05</v>
+      </c>
+      <c r="K568" t="n">
+        <v>-24.96</v>
+      </c>
+      <c r="L568" t="n">
+        <v>-24960.65</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>SH600500</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>中化国际</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>1</v>
+      </c>
+      <c r="I569" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="J569" t="n">
+        <v>9</v>
+      </c>
+      <c r="K569" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="L569" t="n">
+        <v>10294.12</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>SZ300706</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>阿石创</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>1410</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>3</v>
+      </c>
+      <c r="I570" t="n">
+        <v>71.61</v>
+      </c>
+      <c r="J570" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="K570" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="L570" t="n">
+        <v>6018.71</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>SZ300334</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>津膜科技</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr"/>
+      <c r="H571" t="n">
+        <v>13</v>
+      </c>
+      <c r="I571" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J571" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="K571" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="L571" t="n">
+        <v>4035.09</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>SH688733</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>壹石通</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>5</v>
+      </c>
+      <c r="I572" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="J572" t="n">
+        <v>42.44</v>
+      </c>
+      <c r="K572" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L572" t="n">
+        <v>6499.37</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>SH600060</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>海信视像</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>19</v>
+      </c>
+      <c r="I573" t="n">
+        <v>28.01</v>
+      </c>
+      <c r="J573" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="K573" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="L573" t="n">
+        <v>-428.42</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>SZ002125</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>湘潭电化</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>-3.41</v>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>5</v>
+      </c>
+      <c r="I574" t="n">
+        <v>18.14</v>
+      </c>
+      <c r="J574" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="K574" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="L574" t="n">
+        <v>11742.01</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>SZ301418</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>协昌科技</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>15</v>
+      </c>
+      <c r="I575" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J575" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="K575" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="L575" t="n">
+        <v>9355.43</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>SZ000608</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>阳光股份</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr"/>
+      <c r="H576" t="n">
+        <v>1</v>
+      </c>
+      <c r="I576" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="J576" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K576" t="n">
+        <v>-10.59</v>
+      </c>
+      <c r="L576" t="n">
+        <v>-10586.55</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>SZ301607</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>富特科技</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>-23.72</v>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>21</v>
+      </c>
+      <c r="I577" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="J577" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="K577" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="L577" t="n">
+        <v>6241.73</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>SZ301072</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>中捷精工</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H578" t="n">
+        <v>21</v>
+      </c>
+      <c r="I578" t="n">
+        <v>33.72</v>
+      </c>
+      <c r="J578" t="n">
+        <v>40.58</v>
+      </c>
+      <c r="K578" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="L578" t="n">
+        <v>20344.01</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>SZ002138</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>顺络电子</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>1305</t>
+        </is>
+      </c>
+      <c r="H579" t="n">
+        <v>1</v>
+      </c>
+      <c r="I579" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="J579" t="n">
+        <v>61.23</v>
+      </c>
+      <c r="K579" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="L579" t="n">
+        <v>8180.21</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>SZ300752</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>隆利科技</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>-28.02</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F567" t="inlineStr">
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H580" t="n">
+        <v>28</v>
+      </c>
+      <c r="I580" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="J580" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="K580" t="n">
+        <v>-10.44</v>
+      </c>
+      <c r="L580" t="n">
+        <v>-10442.83</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>SZ301528</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>多浦乐</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr"/>
+      <c r="H581" t="n">
+        <v>20</v>
+      </c>
+      <c r="I581" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="J581" t="n">
+        <v>64.09</v>
+      </c>
+      <c r="K581" t="n">
+        <v>-28.63</v>
+      </c>
+      <c r="L581" t="n">
+        <v>-28630.29</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>SH600162</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>香江控股</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="H582" t="n">
+        <v>1</v>
+      </c>
+      <c r="I582" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J582" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="K582" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="L582" t="n">
+        <v>6042.3</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>SH605018</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>长华集团</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="H583" t="n">
+        <v>4</v>
+      </c>
+      <c r="I583" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="J583" t="n">
+        <v>19.08</v>
+      </c>
+      <c r="K583" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="L583" t="n">
+        <v>9090.91</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>SZ002645</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>华宏科技</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>-13.24</v>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>0935</t>
+        </is>
+      </c>
+      <c r="H584" t="n">
+        <v>1</v>
+      </c>
+      <c r="I584" t="n">
+        <v>31.32</v>
+      </c>
+      <c r="J584" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="K584" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="L584" t="n">
+        <v>6864.62</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>SH600378</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>昊华科技</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>0935</t>
+        </is>
+      </c>
+      <c r="H585" t="n">
+        <v>3</v>
+      </c>
+      <c r="I585" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="J585" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="K585" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="L585" t="n">
+        <v>7092.53</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>SZ002072</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>凯瑞德</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="G567" t="inlineStr">
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="H586" t="n">
+        <v>18</v>
+      </c>
+      <c r="I586" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="J586" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="K586" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="L586" t="n">
+        <v>7206.21</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>SZ300305</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>裕兴股份</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
         <is>
           <t>0940</t>
         </is>
       </c>
-      <c r="H567" t="n">
-        <v>21</v>
-      </c>
-      <c r="I567" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="J567" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="K567" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="L567" t="n">
-        <v>6886.66</v>
+      <c r="H587" t="n">
+        <v>12</v>
+      </c>
+      <c r="I587" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="J587" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="K587" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="L587" t="n">
+        <v>7190.41</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>SZ300328</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>宜安科技</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr"/>
+      <c r="H588" t="n">
+        <v>5</v>
+      </c>
+      <c r="I588" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="J588" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="K588" t="n">
+        <v>-12.21</v>
+      </c>
+      <c r="L588" t="n">
+        <v>-12211.67</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>SZ301458</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>钧崴电子</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="H589" t="n">
+        <v>1</v>
+      </c>
+      <c r="I589" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="J589" t="n">
+        <v>52.65</v>
+      </c>
+      <c r="K589" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="L589" t="n">
+        <v>6020.94</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>SZ300319</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>麦捷科技</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="H590" t="n">
+        <v>1</v>
+      </c>
+      <c r="I590" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="J590" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="K590" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="L590" t="n">
+        <v>6029.51</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>SZ300930</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>屹通新材</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="H591" t="n">
+        <v>2</v>
+      </c>
+      <c r="I591" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="J591" t="n">
+        <v>37.31</v>
+      </c>
+      <c r="K591" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="L591" t="n">
+        <v>6205.52</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>SZ002815</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>崇达技术</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="H592" t="n">
+        <v>11</v>
+      </c>
+      <c r="I592" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="J592" t="n">
+        <v>18.87</v>
+      </c>
+      <c r="K592" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="L592" t="n">
+        <v>6730.77</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>SZ002823</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>凯中精密</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="H593" t="n">
+        <v>1</v>
+      </c>
+      <c r="I593" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="J593" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="K593" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="L593" t="n">
+        <v>6172.2</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>SZ002608</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>江苏国信</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H594" t="n">
+        <v>28</v>
+      </c>
+      <c r="I594" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="J594" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="K594" t="n">
+        <v>-33.49</v>
+      </c>
+      <c r="L594" t="n">
+        <v>-33494.68</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>SH601001</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>晋控煤业</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr"/>
+      <c r="H595" t="n">
+        <v>12</v>
+      </c>
+      <c r="I595" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="J595" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="K595" t="n">
+        <v>-12.33</v>
+      </c>
+      <c r="L595" t="n">
+        <v>-12331.84</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>SZ002851</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>麦格米特</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="H596" t="n">
+        <v>14</v>
+      </c>
+      <c r="I596" t="n">
+        <v>156.4</v>
+      </c>
+      <c r="J596" t="n">
+        <v>169.07</v>
+      </c>
+      <c r="K596" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="L596" t="n">
+        <v>8101.02</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>SZ300088</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>长信科技</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="H597" t="n">
+        <v>2</v>
+      </c>
+      <c r="I597" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="J597" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="K597" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="L597" t="n">
+        <v>6741.57</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>SZ301577</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>美信科技</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr"/>
+      <c r="H598" t="n">
+        <v>8</v>
+      </c>
+      <c r="I598" t="n">
+        <v>97.02</v>
+      </c>
+      <c r="J598" t="n">
+        <v>88.31999999999999</v>
+      </c>
+      <c r="K598" t="n">
+        <v>-8.970000000000001</v>
+      </c>
+      <c r="L598" t="n">
+        <v>-8967.219999999999</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>SZ300747</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>锐科激光</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr"/>
+      <c r="H599" t="n">
+        <v>26</v>
+      </c>
+      <c r="I599" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="J599" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="K599" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="L599" t="n">
+        <v>6917.32</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>SZ300410</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>正业科技</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H600" t="n">
+        <v>28</v>
+      </c>
+      <c r="I600" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="J600" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="K600" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="L600" t="n">
+        <v>-12697.16</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>SZ300184</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>趋势</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>8.039999999999999</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr"/>
+      <c r="H601" t="n">
+        <v>6</v>
+      </c>
+      <c r="I601" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="J601" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="K601" t="n">
+        <v>-13.96</v>
+      </c>
+      <c r="L601" t="n">
+        <v>-13959.8</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>SH603075</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>热威股份</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H602" t="n">
+        <v>29</v>
+      </c>
+      <c r="I602" t="n">
+        <v>28.34</v>
+      </c>
+      <c r="J602" t="n">
+        <v>22.34</v>
+      </c>
+      <c r="K602" t="n">
+        <v>-21.17</v>
+      </c>
+      <c r="L602" t="n">
+        <v>-21171.49</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>SZ301591</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>肯特股份</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>-14.83</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>0940</t>
+        </is>
+      </c>
+      <c r="H603" t="n">
+        <v>2</v>
+      </c>
+      <c r="I603" t="n">
+        <v>49.98</v>
+      </c>
+      <c r="J603" t="n">
+        <v>53</v>
+      </c>
+      <c r="K603" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="L603" t="n">
+        <v>6042.42</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>SH600027</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>华电国际</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>强势</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="H604" t="n">
+        <v>29</v>
+      </c>
+      <c r="I604" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="J604" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="K604" t="n">
+        <v>-23.88</v>
+      </c>
+      <c r="L604" t="n">
+        <v>-23883.16</v>
       </c>
     </row>
   </sheetData>
